--- a/artfynd/A 27668-2026 artfynd.xlsx
+++ b/artfynd/A 27668-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135448975</v>
+        <v>135472033</v>
       </c>
       <c r="B5" t="n">
-        <v>56915</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,16 +1037,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100088</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,19 +1054,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472373</v>
+        <v>472415</v>
       </c>
       <c r="R5" t="n">
-        <v>6550652</v>
+        <v>6550563</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1105,22 +1096,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre födohack vid basen av död tallstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,27 +1143,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135448475</v>
+        <v>135448975</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>56915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100088</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1175,25 +1171,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472327</v>
+        <v>472373</v>
       </c>
       <c r="R6" t="n">
-        <v>6550486</v>
+        <v>6550652</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1225,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,12 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack med stelnade kåda i hackhålen. Små hackhål på rad. Syns med kikare ca 1 m ovanför sveaskogs snitsling.</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,7 +1264,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135448848</v>
+        <v>135448475</v>
       </c>
       <c r="B7" t="n">
         <v>57975</v>
@@ -1300,20 +1297,20 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472361</v>
+        <v>472327</v>
       </c>
       <c r="R7" t="n">
-        <v>6550651</v>
+        <v>6550486</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1345,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1352,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack med savflöde längs med hela granen. Gran märkt med rött band. Svårt med fotoljuset.</t>
+          <t>Ringhack med stelnade kåda i hackhålen. Små hackhål på rad. Syns med kikare ca 1 m ovanför sveaskogs snitsling.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,7 +1384,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135448968</v>
+        <v>135448848</v>
       </c>
       <c r="B8" t="n">
         <v>57975</v>
@@ -1420,7 +1417,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1430,10 +1427,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472356</v>
+        <v>472361</v>
       </c>
       <c r="R8" t="n">
-        <v>6550645</v>
+        <v>6550651</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1465,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,12 +1472,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack med stelnade kåda i hackringarna. Små hackhål på rad, Syns tydligt med kikare ca 5-6 m upp. Gran märkt med rött band.Svårt fotoljus i solen.</t>
+          <t>Rikligt med färska ringhack med savflöde längs med hela granen. Gran märkt med rött band. Svårt med fotoljuset.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,45 +1504,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135448613</v>
+        <v>135448968</v>
       </c>
       <c r="B9" t="n">
-        <v>98060</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bergslagsleden, Bergslagsleden, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472353</v>
+        <v>472356</v>
       </c>
       <c r="R9" t="n">
-        <v>6550555</v>
+        <v>6550645</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1577,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1592,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack med stelnade kåda i hackringarna. Små hackhål på rad, Syns tydligt med kikare ca 5-6 m upp. Gran märkt med rött band.Svårt fotoljus i solen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135448650</v>
+        <v>135470977</v>
       </c>
       <c r="B10" t="n">
-        <v>98063</v>
+        <v>57162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,34 +1635,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergslagsleden, Bergslagsleden, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472366</v>
+        <v>472513</v>
       </c>
       <c r="R10" t="n">
-        <v>6550561</v>
+        <v>6550575</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1679,22 +1694,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,6 +1738,1640 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135472072</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>472386</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6550663</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På stigen</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135472106</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>472385</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6550664</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 stänglar.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135448613</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>472353</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6550555</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135470383</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>472404</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6550636</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135470516</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>472442</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6550600</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135470930</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>472506</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6550575</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135471062</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>472518</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6550601</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135448650</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>472366</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6550561</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135470340</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>472380</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6550687</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135470448</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>472409</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6550638</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135470483</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>472432</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6550624</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135470505</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>472428</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6550608</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135470520</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>472443</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6550598</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135470951</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>472511</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6550575</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135471033</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>472516</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6550601</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27668-2026 artfynd.xlsx
+++ b/artfynd/A 27668-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448639</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135449212</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135449251</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135472033</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448975</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1381,6 +1411,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448475</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1501,6 +1536,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448848</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1621,6 +1661,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448968</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1738,6 +1783,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470977</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1855,6 +1905,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135472072</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1981,6 +2036,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135472106</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2088,6 +2148,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448613</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2195,6 +2260,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470383</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2302,6 +2372,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470516</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2409,6 +2484,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470930</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2516,6 +2596,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471062</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2623,6 +2708,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448650</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2730,6 +2820,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470340</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2837,6 +2932,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470448</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2944,6 +3044,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470483</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3051,6 +3156,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470505</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3158,6 +3268,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470520</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3265,6 +3380,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470951</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3372,8 +3492,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471033</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27668-2026 artfynd.xlsx
+++ b/artfynd/A 27668-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135448639</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135449212</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135449251</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>135472033</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>135448975</v>
       </c>
       <c r="B6" t="n">
-        <v>56915</v>
+        <v>56920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135448475</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>135448848</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>135448968</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>135470977</v>
       </c>
       <c r="B10" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>135472072</v>
       </c>
       <c r="B11" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135472106</v>
       </c>
       <c r="B12" t="n">
-        <v>106324</v>
+        <v>106379</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135448613</v>
       </c>
       <c r="B13" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135470383</v>
       </c>
       <c r="B14" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135470516</v>
       </c>
       <c r="B15" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135470930</v>
       </c>
       <c r="B16" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135471062</v>
       </c>
       <c r="B17" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>135448650</v>
       </c>
       <c r="B18" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>135470340</v>
       </c>
       <c r="B19" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135470448</v>
       </c>
       <c r="B20" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135470483</v>
       </c>
       <c r="B21" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>135470505</v>
       </c>
       <c r="B22" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>135470520</v>
       </c>
       <c r="B23" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>135470951</v>
       </c>
       <c r="B24" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>135471033</v>
       </c>
       <c r="B25" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27668-2026 artfynd.xlsx
+++ b/artfynd/A 27668-2026 artfynd.xlsx
@@ -1916,7 +1916,7 @@
         <v>135472106</v>
       </c>
       <c r="B12" t="n">
-        <v>106379</v>
+        <v>106406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135448613</v>
       </c>
       <c r="B13" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135470383</v>
       </c>
       <c r="B14" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135470516</v>
       </c>
       <c r="B15" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135470930</v>
       </c>
       <c r="B16" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135471062</v>
       </c>
       <c r="B17" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>135448650</v>
       </c>
       <c r="B18" t="n">
-        <v>98107</v>
+        <v>98134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>135470340</v>
       </c>
       <c r="B19" t="n">
-        <v>98107</v>
+        <v>98134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135470448</v>
       </c>
       <c r="B20" t="n">
-        <v>98107</v>
+        <v>98134</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135470483</v>
       </c>
       <c r="B21" t="n">
-        <v>98107</v>
+        <v>98134</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>135470505</v>
       </c>
       <c r="B22" t="n">
-        <v>98107</v>
+        <v>98134</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>135470520</v>
       </c>
       <c r="B23" t="n">
-        <v>98107</v>
+        <v>98134</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>135470951</v>
       </c>
       <c r="B24" t="n">
-        <v>98107</v>
+        <v>98134</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>135471033</v>
       </c>
       <c r="B25" t="n">
-        <v>98107</v>
+        <v>98134</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 27668-2026 artfynd.xlsx
+++ b/artfynd/A 27668-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135448975</v>
+        <v>135914887</v>
       </c>
       <c r="B6" t="n">
-        <v>56920</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,16 +1179,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100088</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1196,19 +1196,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="I6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1217,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472373</v>
+        <v>472457</v>
       </c>
       <c r="R6" t="n">
-        <v>6550652</v>
+        <v>6550573</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1247,22 +1238,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,33 +1279,33 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135448975</t>
+          <t>https://artportalen.se/Sighting/135914887</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135448475</v>
+        <v>135448975</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>56920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100088</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1322,25 +1313,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472327</v>
+        <v>472373</v>
       </c>
       <c r="R7" t="n">
-        <v>6550486</v>
+        <v>6550652</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1372,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,12 +1379,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack med stelnade kåda i hackhålen. Små hackhål på rad. Syns med kikare ca 1 m ovanför sveaskogs snitsling.</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,13 +1405,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135448475</t>
+          <t>https://artportalen.se/Sighting/135448975</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135448848</v>
+        <v>135448475</v>
       </c>
       <c r="B8" t="n">
         <v>57980</v>
@@ -1458,14 +1450,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472361</v>
+        <v>472327</v>
       </c>
       <c r="R8" t="n">
-        <v>6550651</v>
+        <v>6550486</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1497,7 +1489,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1507,12 +1499,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack med savflöde längs med hela granen. Gran märkt med rött band. Svårt med fotoljuset.</t>
+          <t>Ringhack med stelnade kåda i hackhålen. Små hackhål på rad. Syns med kikare ca 1 m ovanför sveaskogs snitsling.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,13 +1530,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135448848</t>
+          <t>https://artportalen.se/Sighting/135448475</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135448968</v>
+        <v>135448848</v>
       </c>
       <c r="B9" t="n">
         <v>57980</v>
@@ -1587,10 +1579,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472356</v>
+        <v>472361</v>
       </c>
       <c r="R9" t="n">
-        <v>6550645</v>
+        <v>6550651</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1622,7 +1614,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1632,12 +1624,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack med stelnade kåda i hackringarna. Små hackhål på rad, Syns tydligt med kikare ca 5-6 m upp. Gran märkt med rött band.Svårt fotoljus i solen.</t>
+          <t>Rikligt med färska ringhack med savflöde längs med hela granen. Gran märkt med rött band. Svårt med fotoljuset.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1663,56 +1655,59 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135448968</t>
+          <t>https://artportalen.se/Sighting/135448848</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135470977</v>
+        <v>135448968</v>
       </c>
       <c r="B10" t="n">
-        <v>57167</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergslagsleden, Bergslagsleden, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472513</v>
+        <v>472356</v>
       </c>
       <c r="R10" t="n">
-        <v>6550575</v>
+        <v>6550645</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1739,27 +1734,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På sten</t>
+          <t>Ringhack med stelnade kåda i hackringarna. Små hackhål på rad, Syns tydligt med kikare ca 5-6 m upp. Gran märkt med rött band.Svårt fotoljus i solen.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1785,13 +1780,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135470977</t>
+          <t>https://artportalen.se/Sighting/135448968</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135472072</v>
+        <v>135470977</v>
       </c>
       <c r="B11" t="n">
         <v>57167</v>
@@ -1831,10 +1826,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472386</v>
+        <v>472513</v>
       </c>
       <c r="R11" t="n">
-        <v>6550663</v>
+        <v>6550575</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1866,7 +1861,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1876,12 +1871,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På stigen</t>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1907,53 +1902,44 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135472072</t>
+          <t>https://artportalen.se/Sighting/135470977</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135760884</v>
+        <v>135472072</v>
       </c>
       <c r="B12" t="n">
-        <v>58141</v>
+        <v>57167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1962,10 +1948,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472375</v>
+        <v>472386</v>
       </c>
       <c r="R12" t="n">
-        <v>6550600</v>
+        <v>6550663</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1992,22 +1978,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På stigen</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2033,53 +2024,44 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135760884</t>
+          <t>https://artportalen.se/Sighting/135472072</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135472106</v>
+        <v>135914826</v>
       </c>
       <c r="B13" t="n">
-        <v>106411</v>
+        <v>58524</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>102990</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2088,10 +2070,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472385</v>
+        <v>472457</v>
       </c>
       <c r="R13" t="n">
-        <v>6550664</v>
+        <v>6550573</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2118,27 +2100,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:54</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2 stänglar.</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2164,51 +2141,65 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135472106</t>
+          <t>https://artportalen.se/Sighting/135914826</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135448613</v>
+        <v>135760884</v>
       </c>
       <c r="B14" t="n">
-        <v>98136</v>
+        <v>58141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergslagsleden, Bergslagsleden, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472353</v>
+        <v>472375</v>
       </c>
       <c r="R14" t="n">
-        <v>6550555</v>
+        <v>6550600</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2235,22 +2226,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2276,51 +2267,56 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135448613</t>
+          <t>https://artportalen.se/Sighting/135760884</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135470383</v>
+        <v>135914970</v>
       </c>
       <c r="B15" t="n">
-        <v>98136</v>
+        <v>58141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bergslagsleden, Bergslagsleden, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472404</v>
+        <v>472457</v>
       </c>
       <c r="R15" t="n">
-        <v>6550636</v>
+        <v>6550573</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2347,22 +2343,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2388,16 +2384,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135470383</t>
+          <t>https://artportalen.se/Sighting/135914970</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135470516</v>
+        <v>135915114</v>
       </c>
       <c r="B16" t="n">
-        <v>98136</v>
+        <v>58136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,34 +2401,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>103023</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergslagsleden, Bergslagsleden, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472442</v>
+        <v>472457</v>
       </c>
       <c r="R16" t="n">
-        <v>6550600</v>
+        <v>6550573</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2459,22 +2460,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2500,16 +2501,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135470516</t>
+          <t>https://artportalen.se/Sighting/135915114</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135470930</v>
+        <v>135472106</v>
       </c>
       <c r="B17" t="n">
-        <v>98136</v>
+        <v>106413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,34 +2518,48 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergslagsleden, Bergslagsleden, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472506</v>
+        <v>472385</v>
       </c>
       <c r="R17" t="n">
-        <v>6550575</v>
+        <v>6550664</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2576,7 +2591,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2586,7 +2601,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 stänglar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2612,16 +2632,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135470930</t>
+          <t>https://artportalen.se/Sighting/135472106</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135471062</v>
+        <v>135448613</v>
       </c>
       <c r="B18" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2653,10 +2673,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472518</v>
+        <v>472353</v>
       </c>
       <c r="R18" t="n">
-        <v>6550601</v>
+        <v>6550555</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2683,22 +2703,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2724,16 +2744,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471062</t>
+          <t>https://artportalen.se/Sighting/135448613</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135448650</v>
+        <v>135470383</v>
       </c>
       <c r="B19" t="n">
-        <v>98139</v>
+        <v>98138</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,16 +2761,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2765,10 +2785,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472366</v>
+        <v>472404</v>
       </c>
       <c r="R19" t="n">
-        <v>6550561</v>
+        <v>6550636</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2795,22 +2815,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2836,16 +2856,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135448650</t>
+          <t>https://artportalen.se/Sighting/135470383</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135470340</v>
+        <v>135470516</v>
       </c>
       <c r="B20" t="n">
-        <v>98139</v>
+        <v>98138</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,16 +2873,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2877,10 +2897,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472380</v>
+        <v>472442</v>
       </c>
       <c r="R20" t="n">
-        <v>6550687</v>
+        <v>6550600</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2912,7 +2932,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2922,7 +2942,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2948,16 +2968,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135470340</t>
+          <t>https://artportalen.se/Sighting/135470516</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135470448</v>
+        <v>135470930</v>
       </c>
       <c r="B21" t="n">
-        <v>98139</v>
+        <v>98138</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,16 +2985,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2989,10 +3009,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472409</v>
+        <v>472506</v>
       </c>
       <c r="R21" t="n">
-        <v>6550638</v>
+        <v>6550575</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -3024,7 +3044,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3034,7 +3054,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3060,16 +3080,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135470448</t>
+          <t>https://artportalen.se/Sighting/135470930</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135470483</v>
+        <v>135471062</v>
       </c>
       <c r="B22" t="n">
-        <v>98139</v>
+        <v>98138</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3077,16 +3097,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3101,10 +3121,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472432</v>
+        <v>472518</v>
       </c>
       <c r="R22" t="n">
-        <v>6550624</v>
+        <v>6550601</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3136,7 +3156,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3146,7 +3166,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3172,16 +3192,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135470483</t>
+          <t>https://artportalen.se/Sighting/135471062</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135470505</v>
+        <v>135448650</v>
       </c>
       <c r="B23" t="n">
-        <v>98139</v>
+        <v>98141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3213,10 +3233,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472428</v>
+        <v>472366</v>
       </c>
       <c r="R23" t="n">
-        <v>6550608</v>
+        <v>6550561</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3243,22 +3263,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,16 +3304,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135470505</t>
+          <t>https://artportalen.se/Sighting/135448650</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135470520</v>
+        <v>135470340</v>
       </c>
       <c r="B24" t="n">
-        <v>98139</v>
+        <v>98141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3325,10 +3345,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472443</v>
+        <v>472380</v>
       </c>
       <c r="R24" t="n">
-        <v>6550598</v>
+        <v>6550687</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3360,7 +3380,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3370,7 +3390,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3396,16 +3416,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135470520</t>
+          <t>https://artportalen.se/Sighting/135470340</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135470951</v>
+        <v>135470448</v>
       </c>
       <c r="B25" t="n">
-        <v>98139</v>
+        <v>98141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3437,10 +3457,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472511</v>
+        <v>472409</v>
       </c>
       <c r="R25" t="n">
-        <v>6550575</v>
+        <v>6550638</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3472,7 +3492,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3482,7 +3502,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3508,16 +3528,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135470951</t>
+          <t>https://artportalen.se/Sighting/135470448</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135471033</v>
+        <v>135470483</v>
       </c>
       <c r="B26" t="n">
-        <v>98139</v>
+        <v>98141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3549,10 +3569,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>472516</v>
+        <v>472432</v>
       </c>
       <c r="R26" t="n">
-        <v>6550601</v>
+        <v>6550624</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3584,7 +3604,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3594,7 +3614,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3619,6 +3639,454 @@
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470483</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135470505</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98141</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>472428</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6550608</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470505</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135470520</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98141</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>472443</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6550598</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470520</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135470951</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98141</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>472511</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6550575</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470951</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135471033</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98141</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>472516</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6550601</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135471033</t>
         </is>
@@ -3651,6 +4119,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
